--- a/Grids Germany/No leap years/Saxony insights/[Saxony][Euclidean][CI]Yearly_normality.xlsx
+++ b/Grids Germany/No leap years/Saxony insights/[Saxony][Euclidean][CI]Yearly_normality.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,52 +429,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_W</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P1_p</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>P1_Normality</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_W</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Shapiro_P2_p</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>P2_Normality</t>
         </is>
@@ -478,16 +490,16 @@
         <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9724482297897339</v>
+        <v>0.9781045317649841</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2088150680065155</v>
+        <v>0.3991628289222717</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -495,10 +507,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.7968633770942688</v>
+        <v>0.7622050642967224</v>
       </c>
       <c r="I2" t="n">
-        <v>0.004565615206956863</v>
+        <v>0.000894677999895066</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -516,16 +528,16 @@
         <v>1997</v>
       </c>
       <c r="C3" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9560555815696716</v>
+        <v>0.9514895677566528</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03477234020829201</v>
+        <v>0.02480403706431389</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -533,10 +545,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.9457123279571533</v>
+        <v>0.9620356559753418</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4963231086730957</v>
+        <v>0.6988526582717896</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -554,16 +566,16 @@
         <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9749053716659546</v>
+        <v>0.9797908663749695</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2710670232772827</v>
+        <v>0.4667457640171051</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -571,10 +583,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8170945048332214</v>
+        <v>0.8329582810401917</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008184893988072872</v>
+        <v>0.0077246418222785</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -592,16 +604,16 @@
         <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9788220524787903</v>
+        <v>0.9824454784393311</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4034076035022736</v>
+        <v>0.5866261124610901</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -609,10 +621,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.9074445962905884</v>
+        <v>0.9499207139015198</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1446747332811356</v>
+        <v>0.4884316027164459</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -630,16 +642,16 @@
         <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9431977868080139</v>
+        <v>0.9380509257316589</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008967024274170399</v>
+        <v>0.006417678669095039</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -647,14 +659,14 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8634923696517944</v>
+        <v>0.898428738117218</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03403521701693535</v>
+        <v>0.07584866136312485</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -668,16 +680,16 @@
         <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9801768660545349</v>
+        <v>0.9794510006904602</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4592532515525818</v>
+        <v>0.4525354504585266</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -685,10 +697,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8076400756835938</v>
+        <v>0.8473325967788696</v>
       </c>
       <c r="I7" t="n">
-        <v>0.006213414948433638</v>
+        <v>0.01245006639510393</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -706,16 +718,16 @@
         <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9813306331634521</v>
+        <v>0.9800883531570435</v>
       </c>
       <c r="F8" t="n">
-        <v>0.510642409324646</v>
+        <v>0.4794157743453979</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,10 +735,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.9519161581993103</v>
+        <v>0.9327353835105896</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5908325910568237</v>
+        <v>0.2692811787128448</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -744,16 +756,16 @@
         <v>2003</v>
       </c>
       <c r="C9" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>0.947081983089447</v>
+        <v>0.9423491954803467</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01339368894696236</v>
+        <v>0.009799730964004993</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -761,10 +773,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8811711072921753</v>
+        <v>0.8999727368354797</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06039261445403099</v>
+        <v>0.08028789609670639</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -782,16 +794,16 @@
         <v>2004</v>
       </c>
       <c r="C10" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9802410006523132</v>
+        <v>0.9821073412895203</v>
       </c>
       <c r="F10" t="n">
-        <v>0.462020218372345</v>
+        <v>0.5706024765968323</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -799,10 +811,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8498544096946716</v>
+        <v>0.8700442314147949</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02210939861834049</v>
+        <v>0.02723793871700764</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -820,16 +832,16 @@
         <v>2005</v>
       </c>
       <c r="C11" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9630413055419922</v>
+        <v>0.9675700068473816</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0745902955532074</v>
+        <v>0.1359265446662903</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -837,10 +849,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8456223607063293</v>
+        <v>0.8673443198204041</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01937962137162685</v>
+        <v>0.02477228455245495</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -858,16 +870,16 @@
         <v>2006</v>
       </c>
       <c r="C12" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9410468339920044</v>
+        <v>0.9308931231498718</v>
       </c>
       <c r="F12" t="n">
-        <v>0.007203847169876099</v>
+        <v>0.003234168281778693</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -875,10 +887,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.9736557602882385</v>
+        <v>0.989102303981781</v>
       </c>
       <c r="I12" t="n">
-        <v>0.921357274055481</v>
+        <v>0.9986505508422852</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -896,16 +908,16 @@
         <v>2007</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9780029058456421</v>
+        <v>0.977719783782959</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3721449971199036</v>
+        <v>0.384796142578125</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -913,10 +925,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.9777993559837341</v>
+        <v>0.9584978222846985</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9600412845611572</v>
+        <v>0.6346272826194763</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -934,16 +946,16 @@
         <v>2008</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9794372320175171</v>
+        <v>0.9597230553627014</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4281343221664429</v>
+        <v>0.05890680849552155</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -951,10 +963,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.9551247954368591</v>
+        <v>0.951992928981781</v>
       </c>
       <c r="I14" t="n">
-        <v>0.642686665058136</v>
+        <v>0.5219045877456665</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -972,16 +984,16 @@
         <v>2009</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9896043539047241</v>
+        <v>0.9835846424102783</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9008166193962097</v>
+        <v>0.6416653394699097</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -989,10 +1001,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.9499152898788452</v>
+        <v>0.9577178955078125</v>
       </c>
       <c r="I15" t="n">
-        <v>0.559390664100647</v>
+        <v>0.6206371188163757</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1010,16 +1022,16 @@
         <v>2010</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>0.973558783531189</v>
+        <v>0.973798930644989</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2351366281509399</v>
+        <v>0.2607883512973785</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1027,10 +1039,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.9131847023963928</v>
+        <v>0.9385396838188171</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1752801090478897</v>
+        <v>0.3315100073814392</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1048,16 +1060,16 @@
         <v>2011</v>
       </c>
       <c r="C17" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>0.979265034198761</v>
+        <v>0.9686300754547119</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4211065471172333</v>
+        <v>0.1521036177873611</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1065,10 +1077,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.8971114158630371</v>
+        <v>0.9071018695831299</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1024138107895851</v>
+        <v>0.104507677257061</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1086,16 +1098,16 @@
         <v>2012</v>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9497546553611755</v>
+        <v>0.9477290511131287</v>
       </c>
       <c r="F18" t="n">
-        <v>0.01772794872522354</v>
+        <v>0.0168511439114809</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1103,10 +1115,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.9514952301979065</v>
+        <v>0.960663378238678</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5841532349586487</v>
+        <v>0.6738516092300415</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1124,16 +1136,16 @@
         <v>2013</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9353620409965515</v>
+        <v>0.9408430457115173</v>
       </c>
       <c r="F19" t="n">
-        <v>0.004084848333150148</v>
+        <v>0.008440330624580383</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1141,10 +1153,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.9481481313705444</v>
+        <v>0.9485599398612976</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5323423743247986</v>
+        <v>0.4672238826751709</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1162,16 +1174,16 @@
         <v>2014</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9716318845748901</v>
+        <v>0.9744035005569458</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1912351697683334</v>
+        <v>0.2773276269435883</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1179,10 +1191,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.9437726736068726</v>
+        <v>0.9392415285110474</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4687820374965668</v>
+        <v>0.3398269712924957</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1200,16 +1212,16 @@
         <v>2015</v>
       </c>
       <c r="C21" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E21" t="n">
-        <v>0.963729202747345</v>
+        <v>0.9703034162521362</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08045558631420135</v>
+        <v>0.1814714223146439</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1217,10 +1229,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.9490941166877747</v>
+        <v>0.9243647456169128</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5467314720153809</v>
+        <v>0.1982331126928329</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1238,16 +1250,16 @@
         <v>2016</v>
       </c>
       <c r="C22" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9647168517112732</v>
+        <v>0.9673335552215576</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08969694375991821</v>
+        <v>0.1325542330741882</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1255,10 +1267,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.9117972850799561</v>
+        <v>0.9609116315841675</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1673433184623718</v>
+        <v>0.6783715486526489</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1276,16 +1288,16 @@
         <v>2017</v>
       </c>
       <c r="C23" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9673852324485779</v>
+        <v>0.9726459980010986</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1203074604272842</v>
+        <v>0.2316671758890152</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1293,10 +1305,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.9388459324836731</v>
+        <v>0.9286383390426636</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4037349820137024</v>
+        <v>0.2319540232419968</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1314,16 +1326,16 @@
         <v>2018</v>
       </c>
       <c r="C24" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9576734304428101</v>
+        <v>0.9464807510375977</v>
       </c>
       <c r="F24" t="n">
-        <v>0.041444081813097</v>
+        <v>0.01484189834445715</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1331,10 +1343,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.8390282988548279</v>
+        <v>0.8628413677215576</v>
       </c>
       <c r="I24" t="n">
-        <v>0.01581405662000179</v>
+        <v>0.02116923406720161</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1352,16 +1364,16 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9755034446716309</v>
+        <v>0.9766205549240112</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2885258197784424</v>
+        <v>0.3459416627883911</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1369,10 +1381,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.7851132154464722</v>
+        <v>0.8253470063209534</v>
       </c>
       <c r="I25" t="n">
-        <v>0.003285800339654088</v>
+        <v>0.00603360403329134</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1390,16 +1402,16 @@
         <v>2020</v>
       </c>
       <c r="C26" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9604508280754089</v>
+        <v>0.9707933664321899</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05612468719482422</v>
+        <v>0.1910444051027298</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1407,10 +1419,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.970366895198822</v>
+        <v>0.9732389450073242</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8815265893936157</v>
+        <v>0.8879466652870178</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1428,16 +1440,16 @@
         <v>2021</v>
       </c>
       <c r="C27" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9672768712043762</v>
+        <v>0.9673022627830505</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1188830956816673</v>
+        <v>0.1321134716272354</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1445,10 +1457,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.9334220886230469</v>
+        <v>0.940842866897583</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3405416309833527</v>
+        <v>0.3594664335250854</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1466,16 +1478,16 @@
         <v>2022</v>
       </c>
       <c r="C28" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9834654927253723</v>
+        <v>0.9825063943862915</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6132941842079163</v>
+        <v>0.5895304083824158</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1483,10 +1495,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.8976688981056213</v>
+        <v>0.9321878552436829</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1043368577957153</v>
+        <v>0.2639903128147125</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1504,16 +1516,16 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9873376488685608</v>
+        <v>0.9881877303123474</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8056279420852661</v>
+        <v>0.8575549125671387</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1521,10 +1533,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.9350055456161499</v>
+        <v>0.9219684600830078</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3580797016620636</v>
+        <v>0.1814375817775726</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1542,16 +1554,16 @@
         <v>2024</v>
       </c>
       <c r="C30" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9133020639419556</v>
+        <v>0.9131875038146973</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0005252560949884355</v>
+        <v>0.0006573933060280979</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1559,10 +1571,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.8269514441490173</v>
+        <v>0.8266819715499878</v>
       </c>
       <c r="I30" t="n">
-        <v>0.01096715684980154</v>
+        <v>0.006299043539911509</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1580,16 +1592,16 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D31" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9896721839904785</v>
+        <v>0.9903838038444519</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9032512307167053</v>
+        <v>0.9346030950546265</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1597,10 +1609,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.8546768426895142</v>
+        <v>0.8704008460044861</v>
       </c>
       <c r="I31" t="n">
-        <v>0.02572299353778362</v>
+        <v>0.02758249081671238</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1618,16 +1630,16 @@
         <v>1996</v>
       </c>
       <c r="C32" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D32" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9267997741699219</v>
+        <v>0.913299560546875</v>
       </c>
       <c r="F32" t="n">
-        <v>0.001792281749658287</v>
+        <v>0.0006637661717832088</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1635,10 +1647,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.8841097354888916</v>
+        <v>0.8946090936660767</v>
       </c>
       <c r="I32" t="n">
-        <v>0.06652431935071945</v>
+        <v>0.06592016667127609</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1656,16 +1668,16 @@
         <v>1997</v>
       </c>
       <c r="C33" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D33" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9866085648536682</v>
+        <v>0.9893364310264587</v>
       </c>
       <c r="F33" t="n">
-        <v>0.770794689655304</v>
+        <v>0.9013067483901978</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1673,10 +1685,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.9221411347389221</v>
+        <v>0.9475171566009521</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2360277026891708</v>
+        <v>0.4514048397541046</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1694,16 +1706,16 @@
         <v>1998</v>
       </c>
       <c r="C34" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D34" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9793199896812439</v>
+        <v>0.9743563532829285</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4233415126800537</v>
+        <v>0.2760047018527985</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1711,10 +1723,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.9126901626586914</v>
+        <v>0.9146780967712402</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1724099218845367</v>
+        <v>0.138451024889946</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1732,16 +1744,16 @@
         <v>1999</v>
       </c>
       <c r="C35" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D35" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9869945049285889</v>
+        <v>0.9852992296218872</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7894106507301331</v>
+        <v>0.7256618738174438</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1749,10 +1761,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.9505356550216675</v>
+        <v>0.9386292099952698</v>
       </c>
       <c r="I35" t="n">
-        <v>0.5690522193908691</v>
+        <v>0.3325609564781189</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1770,16 +1782,16 @@
         <v>2000</v>
       </c>
       <c r="C36" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D36" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E36" t="n">
-        <v>0.968441367149353</v>
+        <v>0.9671229720115662</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1350922286510468</v>
+        <v>0.1296184808015823</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1787,10 +1799,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.9234288930892944</v>
+        <v>0.9257778525352478</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2462609112262726</v>
+        <v>0.2088294625282288</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1808,16 +1820,16 @@
         <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D37" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9791005849838257</v>
+        <v>0.9808545112609863</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4144719839096069</v>
+        <v>0.5130106210708618</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1825,10 +1837,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.9203794002532959</v>
+        <v>0.9335741996765137</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2226756066083908</v>
+        <v>0.2775735259056091</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -1846,16 +1858,16 @@
         <v>2002</v>
       </c>
       <c r="C38" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D38" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9656330943107605</v>
+        <v>0.9651356935501099</v>
       </c>
       <c r="F38" t="n">
-        <v>0.09921757876873016</v>
+        <v>0.1048858314752579</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1863,10 +1875,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.9300944209098816</v>
+        <v>0.9463735222816467</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3060756921768188</v>
+        <v>0.4344999492168427</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1884,16 +1896,16 @@
         <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D39" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9653748273849487</v>
+        <v>0.9750304222106934</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0964360386133194</v>
+        <v>0.295440286397934</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1901,10 +1913,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.916703462600708</v>
+        <v>0.9369677901268005</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1970946043729782</v>
+        <v>0.3135160803794861</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -1922,16 +1934,16 @@
         <v>2004</v>
       </c>
       <c r="C40" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D40" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9684181809425354</v>
+        <v>0.9694209098815918</v>
       </c>
       <c r="F40" t="n">
-        <v>0.134749710559845</v>
+        <v>0.1653658449649811</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1939,10 +1951,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.8611704111099243</v>
+        <v>0.8806073069572449</v>
       </c>
       <c r="I40" t="n">
-        <v>0.03160254657268524</v>
+        <v>0.03965970873832703</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -1960,16 +1972,16 @@
         <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D41" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9749727845191956</v>
+        <v>0.974118709564209</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2729877829551697</v>
+        <v>0.2694247663021088</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1977,10 +1989,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.903017520904541</v>
+        <v>0.9080830812454224</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1247564107179642</v>
+        <v>0.1083803847432137</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -1998,16 +2010,16 @@
         <v>2006</v>
       </c>
       <c r="C42" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D42" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9631930589675903</v>
+        <v>0.9645452499389648</v>
       </c>
       <c r="F42" t="n">
-        <v>0.07584588229656219</v>
+        <v>0.09848271310329437</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2015,10 +2027,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.9615257382392883</v>
+        <v>0.9594076871871948</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7481333017349243</v>
+        <v>0.65105140209198</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2036,16 +2048,16 @@
         <v>2007</v>
       </c>
       <c r="C43" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D43" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9545615315437317</v>
+        <v>0.9566370844841003</v>
       </c>
       <c r="F43" t="n">
-        <v>0.02959442138671875</v>
+        <v>0.04248881340026855</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2053,10 +2065,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.9474425315856934</v>
+        <v>0.9536721706390381</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5217514634132385</v>
+        <v>0.549997866153717</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2074,16 +2086,16 @@
         <v>2008</v>
       </c>
       <c r="C44" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D44" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E44" t="n">
-        <v>0.975110650062561</v>
+        <v>0.9741445183753967</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2769533097743988</v>
+        <v>0.2701324224472046</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2091,10 +2103,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.9134268164634705</v>
+        <v>0.9157949090003967</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1767026335000992</v>
+        <v>0.1443141549825668</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2112,16 +2124,16 @@
         <v>2009</v>
       </c>
       <c r="C45" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D45" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9805955290794373</v>
+        <v>0.9803043603897095</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4775136709213257</v>
+        <v>0.4887514114379883</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2129,10 +2141,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.9361674189567566</v>
+        <v>0.9238740801811218</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3714240193367004</v>
+        <v>0.1946760416030884</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2150,16 +2162,16 @@
         <v>2010</v>
       </c>
       <c r="C46" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D46" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9717988967895508</v>
+        <v>0.9683040976524353</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1947149038314819</v>
+        <v>0.1469394862651825</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2167,10 +2179,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.8848404288291931</v>
+        <v>0.9003149271011353</v>
       </c>
       <c r="I46" t="n">
-        <v>0.06814682483673096</v>
+        <v>0.08130744844675064</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2188,16 +2200,16 @@
         <v>2011</v>
       </c>
       <c r="C47" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D47" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9681194424629211</v>
+        <v>0.9685747623443604</v>
       </c>
       <c r="F47" t="n">
-        <v>0.130406990647316</v>
+        <v>0.1512148380279541</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2205,10 +2217,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.9223861694335938</v>
+        <v>0.9291346073150635</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2379434257745743</v>
+        <v>0.2362038940191269</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2226,16 +2238,16 @@
         <v>2012</v>
       </c>
       <c r="C48" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D48" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9790319800376892</v>
+        <v>0.9790606498718262</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4117251634597778</v>
+        <v>0.4365755319595337</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2243,10 +2255,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.9365453720092773</v>
+        <v>0.9661883115768433</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3758521676063538</v>
+        <v>0.7737299799919128</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2264,16 +2276,16 @@
         <v>2013</v>
       </c>
       <c r="C49" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D49" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9746851325035095</v>
+        <v>0.9758055806159973</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2648761570453644</v>
+        <v>0.3192272186279297</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2281,10 +2293,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.9406946301460266</v>
+        <v>0.9507620930671692</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4272977113723755</v>
+        <v>0.5018565058708191</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2302,16 +2314,16 @@
         <v>2014</v>
       </c>
       <c r="C50" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D50" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9822959899902344</v>
+        <v>0.9837554693222046</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5560252070426941</v>
+        <v>0.6500192880630493</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2319,10 +2331,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.9744917154312134</v>
+        <v>0.9663797616958618</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9302619099617004</v>
+        <v>0.7771084904670715</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2340,16 +2352,16 @@
         <v>2015</v>
       </c>
       <c r="C51" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D51" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9806352257728577</v>
+        <v>0.9774305820465088</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4792675077915192</v>
+        <v>0.374258816242218</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2357,10 +2369,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.940329909324646</v>
+        <v>0.9295012950897217</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4225679636001587</v>
+        <v>0.2393911331892014</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2378,16 +2390,16 @@
         <v>2016</v>
       </c>
       <c r="C52" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D52" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9820112586021423</v>
+        <v>0.9760006070137024</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5424366593360901</v>
+        <v>0.3254597783088684</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2395,10 +2407,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.8771160840988159</v>
+        <v>0.9446395039558411</v>
       </c>
       <c r="I52" t="n">
-        <v>0.05288008600473404</v>
+        <v>0.409769594669342</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2416,16 +2428,16 @@
         <v>2017</v>
       </c>
       <c r="C53" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D53" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9670931100845337</v>
+        <v>0.9643459916114807</v>
       </c>
       <c r="F53" t="n">
-        <v>0.1165064945816994</v>
+        <v>0.09641110897064209</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2433,10 +2445,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8983739018440247</v>
+        <v>0.9165235757827759</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1068216264247894</v>
+        <v>0.1482719480991364</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2454,16 +2466,16 @@
         <v>2018</v>
       </c>
       <c r="C54" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D54" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9690719842910767</v>
+        <v>0.9701383709907532</v>
       </c>
       <c r="F54" t="n">
-        <v>0.1447506546974182</v>
+        <v>0.1783502995967865</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2471,10 +2483,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.8923091888427734</v>
+        <v>0.895005464553833</v>
       </c>
       <c r="I54" t="n">
-        <v>0.08727547526359558</v>
+        <v>0.06688497215509415</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2492,16 +2504,16 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D55" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9711921811103821</v>
+        <v>0.9694440960884094</v>
       </c>
       <c r="F55" t="n">
-        <v>0.1823505759239197</v>
+        <v>0.1657711714506149</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2509,10 +2521,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.9678765535354614</v>
+        <v>0.9649649262428284</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8470331430435181</v>
+        <v>0.7519351243972778</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2530,16 +2542,16 @@
         <v>2020</v>
       </c>
       <c r="C56" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D56" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9734398126602173</v>
+        <v>0.972909688949585</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2321786731481552</v>
+        <v>0.2380560785531998</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2547,10 +2559,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.9337339997291565</v>
+        <v>0.9502905607223511</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3439378440380096</v>
+        <v>0.4943037033081055</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2568,16 +2580,16 @@
         <v>2021</v>
       </c>
       <c r="C57" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D57" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9863676428794861</v>
+        <v>0.9854381084442139</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7590067982673645</v>
+        <v>0.7324107885360718</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2585,10 +2597,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.9726973176002502</v>
+        <v>0.9714543223381042</v>
       </c>
       <c r="I57" t="n">
-        <v>0.910510778427124</v>
+        <v>0.8615826368331909</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2606,16 +2618,16 @@
         <v>2022</v>
       </c>
       <c r="C58" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D58" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9437644481658936</v>
+        <v>0.9389768242835999</v>
       </c>
       <c r="F58" t="n">
-        <v>0.009503092616796494</v>
+        <v>0.007025122176855803</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2623,10 +2635,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.9755489230155945</v>
+        <v>0.9784808754920959</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9407470226287842</v>
+        <v>0.9503942131996155</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2644,16 +2656,16 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D59" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9582293629646301</v>
+        <v>0.952186107635498</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0440293624997139</v>
+        <v>0.02666245959699154</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2661,10 +2673,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.9239050149917603</v>
+        <v>0.9153151512145996</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2501476109027863</v>
+        <v>0.1417656540870667</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2682,16 +2694,16 @@
         <v>2024</v>
       </c>
       <c r="C60" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D60" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9765034914016724</v>
+        <v>0.9742833971977234</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3198810815811157</v>
+        <v>0.2739704847335815</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2699,10 +2711,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.9545741081237793</v>
+        <v>0.9486498832702637</v>
       </c>
       <c r="I60" t="n">
-        <v>0.6336879730224609</v>
+        <v>0.4686056971549988</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2720,16 +2732,16 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D61" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9509303569793701</v>
+        <v>0.9378179907798767</v>
       </c>
       <c r="F61" t="n">
-        <v>0.0200762115418911</v>
+        <v>0.006273720413446426</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2737,10 +2749,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.9717237949371338</v>
+        <v>0.9767662882804871</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8988333940505981</v>
+        <v>0.9327281713485718</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2758,16 +2770,16 @@
         <v>1996</v>
       </c>
       <c r="C62" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D62" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9065862894058228</v>
+        <v>0.9089072346687317</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0002939497062470764</v>
+        <v>0.0004564880218822509</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2775,10 +2787,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.966015100479126</v>
+        <v>0.9827459454536438</v>
       </c>
       <c r="I62" t="n">
-        <v>0.81935054063797</v>
+        <v>0.9815755486488342</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2796,16 +2808,16 @@
         <v>1997</v>
       </c>
       <c r="C63" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D63" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9764194488525391</v>
+        <v>0.9778344035148621</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3171392679214478</v>
+        <v>0.3890348672866821</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2813,10 +2825,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.8973328471183777</v>
+        <v>0.8994580507278442</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1031732484698296</v>
+        <v>0.07877910137176514</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2834,16 +2846,16 @@
         <v>1998</v>
       </c>
       <c r="C64" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D64" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9677233099937439</v>
+        <v>0.9679169058799744</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1248585879802704</v>
+        <v>0.1410277038812637</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2851,10 +2863,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.9516510963439941</v>
+        <v>0.9531305432319641</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5866228938102722</v>
+        <v>0.5408470630645752</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2872,16 +2884,16 @@
         <v>1999</v>
       </c>
       <c r="C65" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D65" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9760844111442566</v>
+        <v>0.9699985384941101</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3064058721065521</v>
+        <v>0.1757466048002243</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2889,10 +2901,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.9843286871910095</v>
+        <v>0.9178692698478699</v>
       </c>
       <c r="I65" t="n">
-        <v>0.9925920367240906</v>
+        <v>0.1558662354946136</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2910,16 +2922,16 @@
         <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D66" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9588164687156677</v>
+        <v>0.956040620803833</v>
       </c>
       <c r="F66" t="n">
-        <v>0.04693989083170891</v>
+        <v>0.03990083560347557</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2927,10 +2939,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.9849251508712769</v>
+        <v>0.9837281107902527</v>
       </c>
       <c r="I66" t="n">
-        <v>0.9940185546875</v>
+        <v>0.9862323999404907</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2948,16 +2960,16 @@
         <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D67" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9226860404014587</v>
+        <v>0.9142293334007263</v>
       </c>
       <c r="F67" t="n">
-        <v>0.00122195144649595</v>
+        <v>0.0007192484335973859</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2965,10 +2977,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.969731330871582</v>
+        <v>0.9850751757621765</v>
       </c>
       <c r="I67" t="n">
-        <v>0.873039186000824</v>
+        <v>0.9912369251251221</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -2986,16 +2998,16 @@
         <v>2002</v>
       </c>
       <c r="C68" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D68" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E68" t="n">
-        <v>0.957973301410675</v>
+        <v>0.9561906456947327</v>
       </c>
       <c r="F68" t="n">
-        <v>0.04281865060329437</v>
+        <v>0.04053618386387825</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3003,10 +3015,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.9554333090782166</v>
+        <v>0.9654216766357422</v>
       </c>
       <c r="I68" t="n">
-        <v>0.6477416753768921</v>
+        <v>0.760110080242157</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3024,16 +3036,16 @@
         <v>2003</v>
       </c>
       <c r="C69" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D69" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9785534143447876</v>
+        <v>0.9759974479675293</v>
       </c>
       <c r="F69" t="n">
-        <v>0.3929446637630463</v>
+        <v>0.3253585994243622</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3041,10 +3053,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.9454833269119263</v>
+        <v>0.9452372789382935</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4930164813995361</v>
+        <v>0.4181710779666901</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3062,16 +3074,16 @@
         <v>2004</v>
       </c>
       <c r="C70" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D70" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9632232785224915</v>
+        <v>0.9694875478744507</v>
       </c>
       <c r="F70" t="n">
-        <v>0.07609833031892776</v>
+        <v>0.1665327399969101</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3079,10 +3091,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.7792688608169556</v>
+        <v>0.7819132208824158</v>
       </c>
       <c r="I70" t="n">
-        <v>0.002797339810058475</v>
+        <v>0.001582218217663467</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3100,16 +3112,16 @@
         <v>2005</v>
       </c>
       <c r="C71" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D71" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9390441179275513</v>
+        <v>0.9408477544784546</v>
       </c>
       <c r="F71" t="n">
-        <v>0.005887744016945362</v>
+        <v>0.008444291539490223</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3117,10 +3129,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.9086250066757202</v>
+        <v>0.9125162363052368</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1505026817321777</v>
+        <v>0.1277679800987244</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3138,16 +3150,16 @@
         <v>2006</v>
       </c>
       <c r="C72" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D72" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9408273696899414</v>
+        <v>0.958069384098053</v>
       </c>
       <c r="F72" t="n">
-        <v>0.007045637350529432</v>
+        <v>0.04943085089325905</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3155,10 +3167,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.8466727733612061</v>
+        <v>0.7016003131866455</v>
       </c>
       <c r="I72" t="n">
-        <v>0.0200220849364996</v>
+        <v>0.0001757462741807103</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3176,27 +3188,27 @@
         <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D73" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9585186243057251</v>
+        <v>0.9593470692634583</v>
       </c>
       <c r="F73" t="n">
-        <v>0.04543947800993919</v>
+        <v>0.0566009022295475</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.9379987120628357</v>
+        <v>0.9380325078964233</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3932813704013824</v>
+        <v>0.3256087005138397</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3214,16 +3226,16 @@
         <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D74" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9342194795608521</v>
+        <v>0.9228236675262451</v>
       </c>
       <c r="F74" t="n">
-        <v>0.003651883685961366</v>
+        <v>0.001537495176307857</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3231,10 +3243,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.9056258201599121</v>
+        <v>0.9012476205825806</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1361328214406967</v>
+        <v>0.08415419608354568</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3252,27 +3264,27 @@
         <v>2009</v>
       </c>
       <c r="C75" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D75" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9449262619018555</v>
+        <v>0.9673888683319092</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0107099637389183</v>
+        <v>0.1333355605602264</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.8109763860702515</v>
+        <v>0.8538521528244019</v>
       </c>
       <c r="I75" t="n">
-        <v>0.006844162009656429</v>
+        <v>0.01553155388683081</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3290,16 +3302,16 @@
         <v>2010</v>
       </c>
       <c r="C76" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D76" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9655399918556213</v>
+        <v>0.9659461379051208</v>
       </c>
       <c r="F76" t="n">
-        <v>0.09820585697889328</v>
+        <v>0.1143529489636421</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3307,10 +3319,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.9387560486793518</v>
+        <v>0.9636831879615784</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4026159942150116</v>
+        <v>0.7288118600845337</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3328,16 +3340,16 @@
         <v>2011</v>
       </c>
       <c r="C77" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D77" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9721322655677795</v>
+        <v>0.9662229418754578</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2018383741378784</v>
+        <v>0.1177765056490898</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3345,10 +3357,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.9655757546424866</v>
+        <v>0.967037558555603</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8126233816146851</v>
+        <v>0.7886401414871216</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3366,16 +3378,16 @@
         <v>2012</v>
       </c>
       <c r="C78" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D78" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9141784310340881</v>
+        <v>0.9288968443870544</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0005673972773365676</v>
+        <v>0.002683152910321951</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3383,10 +3395,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.9844567179679871</v>
+        <v>0.9886438250541687</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9929164052009583</v>
+        <v>0.9982399344444275</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3404,27 +3416,27 @@
         <v>2013</v>
       </c>
       <c r="C79" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D79" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9674063324928284</v>
+        <v>0.9538594484329224</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1205865517258644</v>
+        <v>0.03174096345901489</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.9760348796844482</v>
+        <v>0.9590609669685364</v>
       </c>
       <c r="I79" t="n">
-        <v>0.9452669024467468</v>
+        <v>0.6447808742523193</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3442,16 +3454,16 @@
         <v>2014</v>
       </c>
       <c r="C80" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D80" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9804920554161072</v>
+        <v>0.9750462770462036</v>
       </c>
       <c r="F80" t="n">
-        <v>0.4729581475257874</v>
+        <v>0.2959110736846924</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3459,10 +3471,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.9323301911354065</v>
+        <v>0.9363045692443848</v>
       </c>
       <c r="I80" t="n">
-        <v>0.328879177570343</v>
+        <v>0.3061833083629608</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3480,16 +3492,16 @@
         <v>2015</v>
       </c>
       <c r="C81" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D81" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9381632804870605</v>
+        <v>0.9439493417739868</v>
       </c>
       <c r="F81" t="n">
-        <v>0.00539134256541729</v>
+        <v>0.01149811316281557</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3497,10 +3509,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.9293680787086487</v>
+        <v>0.9242903590202332</v>
       </c>
       <c r="I81" t="n">
-        <v>0.2989737987518311</v>
+        <v>0.1976899951696396</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3518,16 +3530,16 @@
         <v>2016</v>
       </c>
       <c r="C82" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D82" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E82" t="n">
-        <v>0.9735077619552612</v>
+        <v>0.9646191596984863</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2338639944791794</v>
+        <v>0.09926222264766693</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3535,10 +3547,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.9119969010353088</v>
+        <v>0.9212559461593628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.168463334441185</v>
+        <v>0.1767157465219498</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3556,16 +3568,16 @@
         <v>2017</v>
       </c>
       <c r="C83" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D83" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E83" t="n">
-        <v>0.9572272300720215</v>
+        <v>0.9569042921066284</v>
       </c>
       <c r="F83" t="n">
-        <v>0.03948202729225159</v>
+        <v>0.04370349645614624</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3573,10 +3585,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.9290781617164612</v>
+        <v>0.9015680551528931</v>
       </c>
       <c r="I83" t="n">
-        <v>0.296179860830307</v>
+        <v>0.08515574038028717</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3594,16 +3606,16 @@
         <v>2018</v>
       </c>
       <c r="C84" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D84" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E84" t="n">
-        <v>0.9801052808761597</v>
+        <v>0.9814403653144836</v>
       </c>
       <c r="F84" t="n">
-        <v>0.456175833940506</v>
+        <v>0.5395672917366028</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3611,10 +3623,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.9183768630027771</v>
+        <v>0.9102041721343994</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2083696275949478</v>
+        <v>0.1172560751438141</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3632,16 +3644,16 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D85" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9743695259094238</v>
+        <v>0.9767220020294189</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2562205791473389</v>
+        <v>0.3493912816047668</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3649,10 +3661,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.9557943344116211</v>
+        <v>0.9466238021850586</v>
       </c>
       <c r="I85" t="n">
-        <v>0.6536681652069092</v>
+        <v>0.4381592273712158</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3670,27 +3682,27 @@
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D86" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E86" t="n">
-        <v>0.9614697694778442</v>
+        <v>0.9495275616645813</v>
       </c>
       <c r="F86" t="n">
-        <v>0.06275950372219086</v>
+        <v>0.02025806903839111</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.8392065763473511</v>
+        <v>0.8492252230644226</v>
       </c>
       <c r="I86" t="n">
-        <v>0.01590072922408581</v>
+        <v>0.01327157579362392</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -3708,16 +3720,16 @@
         <v>2021</v>
       </c>
       <c r="C87" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D87" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9663252234458923</v>
+        <v>0.9716113805770874</v>
       </c>
       <c r="F87" t="n">
-        <v>0.1070712730288506</v>
+        <v>0.2080891281366348</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3725,10 +3737,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>0.9637293815612793</v>
+        <v>0.9457469582557678</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7836980223655701</v>
+        <v>0.4254379868507385</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -3746,16 +3758,16 @@
         <v>2022</v>
       </c>
       <c r="C88" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D88" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E88" t="n">
-        <v>0.9804460406303406</v>
+        <v>0.9793185591697693</v>
       </c>
       <c r="F88" t="n">
-        <v>0.4709413349628448</v>
+        <v>0.4470763802528381</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3763,10 +3775,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>0.9676216244697571</v>
+        <v>0.9695289134979248</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8433278799057007</v>
+        <v>0.8309210538864136</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -3784,16 +3796,16 @@
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D89" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9795103073120117</v>
+        <v>0.9749782681465149</v>
       </c>
       <c r="F89" t="n">
-        <v>0.431143194437027</v>
+        <v>0.2938952445983887</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3801,14 +3813,14 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>0.9424606561660767</v>
+        <v>0.8368399143218994</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4507598280906677</v>
+        <v>0.008775132708251476</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -3822,16 +3834,16 @@
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D90" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9831218719482422</v>
+        <v>0.988243579864502</v>
       </c>
       <c r="F90" t="n">
-        <v>0.5962563753128052</v>
+        <v>0.8598331212997437</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3839,10 +3851,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>0.9598404765129089</v>
+        <v>0.9364659190177917</v>
       </c>
       <c r="I90" t="n">
-        <v>0.7204660773277283</v>
+        <v>0.3079535067081451</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -3860,16 +3872,16 @@
         <v>2025</v>
       </c>
       <c r="C91" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D91" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E91" t="n">
-        <v>0.975452721118927</v>
+        <v>0.9784017205238342</v>
       </c>
       <c r="F91" t="n">
-        <v>0.2870077788829803</v>
+        <v>0.4105322659015656</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3877,10 +3889,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>0.8833082318305969</v>
+        <v>0.9117749333381653</v>
       </c>
       <c r="I91" t="n">
-        <v>0.06479040533304214</v>
+        <v>0.1242982745170593</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -3898,16 +3910,16 @@
         <v>1996</v>
       </c>
       <c r="C92" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D92" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E92" t="n">
-        <v>0.9428964853286743</v>
+        <v>0.9394626617431641</v>
       </c>
       <c r="F92" t="n">
-        <v>0.008694941177964211</v>
+        <v>0.007367742713540792</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3915,10 +3927,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>0.8189430236816406</v>
+        <v>0.7869829535484314</v>
       </c>
       <c r="I92" t="n">
-        <v>0.008643001317977905</v>
+        <v>0.001838740194216371</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -3936,16 +3948,16 @@
         <v>1997</v>
       </c>
       <c r="C93" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D93" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9456484317779541</v>
+        <v>0.9421370625495911</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0115401353687048</v>
+        <v>0.009595161303877831</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3953,14 +3965,14 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>0.9204361438751221</v>
+        <v>0.8597702980041504</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2230939865112305</v>
+        <v>0.01903226599097252</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -3974,16 +3986,16 @@
         <v>1998</v>
       </c>
       <c r="C94" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D94" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E94" t="n">
-        <v>0.9538277387619019</v>
+        <v>0.9567022323608398</v>
       </c>
       <c r="F94" t="n">
-        <v>0.02735014446079731</v>
+        <v>0.042781762778759</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3991,10 +4003,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>0.8183836936950684</v>
+        <v>0.8417080640792847</v>
       </c>
       <c r="I94" t="n">
-        <v>0.008501569740474224</v>
+        <v>0.01031171716749668</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4012,16 +4024,16 @@
         <v>1999</v>
       </c>
       <c r="C95" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D95" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9756876826286316</v>
+        <v>0.9850068092346191</v>
       </c>
       <c r="F95" t="n">
-        <v>0.2940958738327026</v>
+        <v>0.7113937735557556</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4029,10 +4041,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>0.9557336568832397</v>
+        <v>0.9491899609565735</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6526721715927124</v>
+        <v>0.4769640564918518</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4050,16 +4062,16 @@
         <v>2000</v>
       </c>
       <c r="C96" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D96" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E96" t="n">
-        <v>0.914736807346344</v>
+        <v>0.9097476601600647</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0005961006972938776</v>
+        <v>0.0004900855128653347</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4067,14 +4079,14 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>0.847802996635437</v>
+        <v>0.8962697386741638</v>
       </c>
       <c r="I96" t="n">
-        <v>0.02073865011334419</v>
+        <v>0.07006083428859711</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -4088,16 +4100,16 @@
         <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D97" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E97" t="n">
-        <v>0.9351423382759094</v>
+        <v>0.9363353252410889</v>
       </c>
       <c r="F97" t="n">
-        <v>0.003997582942247391</v>
+        <v>0.005433422513306141</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4105,14 +4117,14 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>0.8767879009246826</v>
+        <v>0.8436290621757507</v>
       </c>
       <c r="I97" t="n">
-        <v>0.05231615900993347</v>
+        <v>0.01099453400820494</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4126,16 +4138,16 @@
         <v>2002</v>
       </c>
       <c r="C98" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D98" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E98" t="n">
-        <v>0.9528025984764099</v>
+        <v>0.9536646008491516</v>
       </c>
       <c r="F98" t="n">
-        <v>0.02450584247708321</v>
+        <v>0.03110150620341301</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4143,10 +4155,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>0.9408548474311829</v>
+        <v>0.9327433109283447</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4293881356716156</v>
+        <v>0.2693584263324738</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -4164,16 +4176,16 @@
         <v>2003</v>
       </c>
       <c r="C99" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D99" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E99" t="n">
-        <v>0.952445924282074</v>
+        <v>0.9397457838058472</v>
       </c>
       <c r="F99" t="n">
-        <v>0.02358976006507874</v>
+        <v>0.007575442083179951</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4181,10 +4193,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>0.8546484112739563</v>
+        <v>0.8754474520683289</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0256999246776104</v>
+        <v>0.03298075497150421</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4202,16 +4214,16 @@
         <v>2004</v>
       </c>
       <c r="C100" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D100" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E100" t="n">
-        <v>0.9759268164634705</v>
+        <v>0.9678409099578857</v>
       </c>
       <c r="F100" t="n">
-        <v>0.3014639317989349</v>
+        <v>0.1398944705724716</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4219,10 +4231,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>0.8324806690216064</v>
+        <v>0.8825231194496155</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0129545284435153</v>
+        <v>0.04248775914311409</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -4240,16 +4252,16 @@
         <v>2005</v>
       </c>
       <c r="C101" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D101" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E101" t="n">
-        <v>0.9330531358718872</v>
+        <v>0.9501795768737793</v>
       </c>
       <c r="F101" t="n">
-        <v>0.003259384538978338</v>
+        <v>0.02166399918496609</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4257,10 +4269,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>0.9454530477523804</v>
+        <v>0.9546815156936646</v>
       </c>
       <c r="I101" t="n">
-        <v>0.4925808310508728</v>
+        <v>0.5672622323036194</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -4278,16 +4290,16 @@
         <v>2006</v>
       </c>
       <c r="C102" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D102" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E102" t="n">
-        <v>0.920113742351532</v>
+        <v>0.9113065004348755</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0009656107285991311</v>
+        <v>0.0005595165421254933</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -4295,10 +4307,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>0.7966015934944153</v>
+        <v>0.8533139228820801</v>
       </c>
       <c r="I102" t="n">
-        <v>0.004531917162239552</v>
+        <v>0.0152488686144352</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4316,16 +4328,16 @@
         <v>2007</v>
       </c>
       <c r="C103" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D103" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9617983102798462</v>
+        <v>0.9617970585823059</v>
       </c>
       <c r="F103" t="n">
-        <v>0.06506476551294327</v>
+        <v>0.07345699518918991</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -4333,10 +4345,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>0.962047815322876</v>
+        <v>0.96526700258255</v>
       </c>
       <c r="I103" t="n">
-        <v>0.7566363215446472</v>
+        <v>0.7573456764221191</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4354,31 +4366,31 @@
         <v>2008</v>
       </c>
       <c r="C104" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D104" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E104" t="n">
-        <v>0.9644516110420227</v>
+        <v>0.9392964243888855</v>
       </c>
       <c r="F104" t="n">
-        <v>0.08711486309766769</v>
+        <v>0.007248586043715477</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>0.9449138641357422</v>
+        <v>0.8512517213821411</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4848584532737732</v>
+        <v>0.0142152551561594</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4392,16 +4404,16 @@
         <v>2009</v>
       </c>
       <c r="C105" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D105" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E105" t="n">
-        <v>0.9862726926803589</v>
+        <v>0.9854753017425537</v>
       </c>
       <c r="F105" t="n">
-        <v>0.7543296217918396</v>
+        <v>0.7342151403427124</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4409,10 +4421,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>0.9190107583999634</v>
+        <v>0.9100695848464966</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2128003984689713</v>
+        <v>0.116671659052372</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -4430,27 +4442,27 @@
         <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D106" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E106" t="n">
-        <v>0.9554828405380249</v>
+        <v>0.9618252515792847</v>
       </c>
       <c r="F106" t="n">
-        <v>0.03268487006425858</v>
+        <v>0.07367796450853348</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>0.8856115937232971</v>
+        <v>0.9132011532783508</v>
       </c>
       <c r="I106" t="n">
-        <v>0.06990371644496918</v>
+        <v>0.131060317158699</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -4468,16 +4480,16 @@
         <v>2011</v>
       </c>
       <c r="C107" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D107" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E107" t="n">
-        <v>0.9761031866073608</v>
+        <v>0.9769458174705505</v>
       </c>
       <c r="F107" t="n">
-        <v>0.3070001900196075</v>
+        <v>0.3570992350578308</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -4485,14 +4497,14 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>0.8756003379821777</v>
+        <v>0.853960394859314</v>
       </c>
       <c r="I107" t="n">
-        <v>0.05032782256603241</v>
+        <v>0.01558904536068439</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4506,16 +4518,16 @@
         <v>2012</v>
       </c>
       <c r="C108" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D108" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E108" t="n">
-        <v>0.9468178749084473</v>
+        <v>0.9491984248161316</v>
       </c>
       <c r="F108" t="n">
-        <v>0.01303016673773527</v>
+        <v>0.01958472840487957</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -4523,10 +4535,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>0.947258472442627</v>
+        <v>0.922380805015564</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5190089344978333</v>
+        <v>0.1842258423566818</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -4544,16 +4556,16 @@
         <v>2013</v>
       </c>
       <c r="C109" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D109" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E109" t="n">
-        <v>0.9047255516052246</v>
+        <v>0.9104340076446533</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0002511132333893329</v>
+        <v>0.0005194615805521607</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -4561,10 +4573,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>0.9589394927024841</v>
+        <v>0.9641174674034119</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7055906057357788</v>
+        <v>0.7366716861724854</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -4582,16 +4594,16 @@
         <v>2014</v>
       </c>
       <c r="C110" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D110" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E110" t="n">
-        <v>0.9597458243370056</v>
+        <v>0.9697293043136597</v>
       </c>
       <c r="F110" t="n">
-        <v>0.05195631459355354</v>
+        <v>0.1708333194255829</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -4599,10 +4611,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>0.9148074388504028</v>
+        <v>0.9209967851638794</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1850314289331436</v>
+        <v>0.1750279515981674</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -4620,16 +4632,16 @@
         <v>2015</v>
       </c>
       <c r="C111" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D111" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E111" t="n">
-        <v>0.9000481367111206</v>
+        <v>0.9096055030822754</v>
       </c>
       <c r="F111" t="n">
-        <v>0.0001700507127679884</v>
+        <v>0.0004842232156079262</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -4637,14 +4649,14 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>0.9399917125701904</v>
+        <v>0.8855843544006348</v>
       </c>
       <c r="I111" t="n">
-        <v>0.4182179570198059</v>
+        <v>0.04745223373174667</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Not normal</t>
         </is>
       </c>
     </row>
@@ -4658,16 +4670,16 @@
         <v>2016</v>
       </c>
       <c r="C112" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D112" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E112" t="n">
-        <v>0.9645810723304749</v>
+        <v>0.9682362675666809</v>
       </c>
       <c r="F112" t="n">
-        <v>0.08836591988801956</v>
+        <v>0.1458865255117416</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -4675,10 +4687,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>0.9422651529312134</v>
+        <v>0.9617591500282288</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4481171667575836</v>
+        <v>0.6938135027885437</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -4696,16 +4708,16 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D113" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E113" t="n">
-        <v>0.9363666772842407</v>
+        <v>0.9350383281707764</v>
       </c>
       <c r="F113" t="n">
-        <v>0.00451023830100894</v>
+        <v>0.004795349203050137</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -4713,10 +4725,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>0.8935231566429138</v>
+        <v>0.8915053606033325</v>
       </c>
       <c r="I113" t="n">
-        <v>0.09087181836366653</v>
+        <v>0.05884611234068871</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -4734,16 +4746,16 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D114" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E114" t="n">
-        <v>0.9464617371559143</v>
+        <v>0.9406692981719971</v>
       </c>
       <c r="F114" t="n">
-        <v>0.01255617570132017</v>
+        <v>0.008296775631606579</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4751,10 +4763,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>0.8380471467971802</v>
+        <v>0.8352044820785522</v>
       </c>
       <c r="I114" t="n">
-        <v>0.01534602139145136</v>
+        <v>0.008315123617649078</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -4772,16 +4784,16 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D115" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E115" t="n">
-        <v>0.9768370985984802</v>
+        <v>0.9754495620727539</v>
       </c>
       <c r="F115" t="n">
-        <v>0.3309583365917206</v>
+        <v>0.3081071674823761</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4789,10 +4801,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>0.9671123623847961</v>
+        <v>0.9201929569244385</v>
       </c>
       <c r="I115" t="n">
-        <v>0.8358405232429504</v>
+        <v>0.1698929667472839</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -4810,27 +4822,27 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D116" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E116" t="n">
-        <v>0.952928900718689</v>
+        <v>0.9588171243667603</v>
       </c>
       <c r="F116" t="n">
-        <v>0.02483901008963585</v>
+        <v>0.05350625514984131</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Not normal</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>0.916663646697998</v>
+        <v>0.9364835023880005</v>
       </c>
       <c r="I116" t="n">
-        <v>0.1968336850404739</v>
+        <v>0.3081467747688293</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -4848,16 +4860,16 @@
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D117" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E117" t="n">
-        <v>0.9821694493293762</v>
+        <v>0.9815327525138855</v>
       </c>
       <c r="F117" t="n">
-        <v>0.5499662160873413</v>
+        <v>0.5438165068626404</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4865,10 +4877,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>0.9108024835586548</v>
+        <v>0.9417347311973572</v>
       </c>
       <c r="I117" t="n">
-        <v>0.1618713289499283</v>
+        <v>0.3708085715770721</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -4886,16 +4898,16 @@
         <v>2022</v>
       </c>
       <c r="C118" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D118" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E118" t="n">
-        <v>0.9531664252281189</v>
+        <v>0.9518880844116211</v>
       </c>
       <c r="F118" t="n">
-        <v>0.02547845803201199</v>
+        <v>0.02585016191005707</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4903,10 +4915,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>0.9119310975074768</v>
+        <v>0.9194866418838501</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1680931448936462</v>
+        <v>0.1655032932758331</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -4924,16 +4936,16 @@
         <v>2023</v>
       </c>
       <c r="C119" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D119" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E119" t="n">
-        <v>0.9708837270736694</v>
+        <v>0.9707238078117371</v>
       </c>
       <c r="F119" t="n">
-        <v>0.1763528287410736</v>
+        <v>0.1896573305130005</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4941,10 +4953,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>0.9101036190986633</v>
+        <v>0.9553025364875793</v>
       </c>
       <c r="I119" t="n">
-        <v>0.1581328809261322</v>
+        <v>0.5780137181282043</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -4962,16 +4974,16 @@
         <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D120" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E120" t="n">
-        <v>0.8803949356079102</v>
+        <v>0.8824974894523621</v>
       </c>
       <c r="F120" t="n">
-        <v>3.611339343478903e-05</v>
+        <v>5.609268555417657e-05</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4979,10 +4991,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>0.9039544463157654</v>
+        <v>0.8946512341499329</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1287287920713425</v>
+        <v>0.06602195650339127</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -5000,16 +5012,16 @@
         <v>2025</v>
       </c>
       <c r="C121" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D121" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E121" t="n">
-        <v>0.9773499369621277</v>
+        <v>0.9799120426177979</v>
       </c>
       <c r="F121" t="n">
-        <v>0.3485980629920959</v>
+        <v>0.4718811810016632</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -5017,10 +5029,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>0.841742992401123</v>
+        <v>0.8471232652664185</v>
       </c>
       <c r="I121" t="n">
-        <v>0.01718964986503124</v>
+        <v>0.01236258912831545</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
